--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -1,29 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\MG\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HaveToTrade\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8C046C-1FBB-4CA5-838A-09B5B642ED3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F21C48D-CD5E-4A66-8A73-FE109B5CEF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="6" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="4485" yWindow="2895" windowWidth="15675" windowHeight="12450" firstSheet="9" activeTab="11" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
-    <sheet name="TextEX" sheetId="1" r:id="rId1"/>
-    <sheet name="TextEX2" sheetId="2" r:id="rId2"/>
-    <sheet name="무뚝뚝거래전잡담" sheetId="3" r:id="rId3"/>
-    <sheet name="화난작별인사" sheetId="4" r:id="rId4"/>
-    <sheet name="무뚝뚝거래거절" sheetId="5" r:id="rId5"/>
-    <sheet name="유쾌한재흥정" sheetId="6" r:id="rId6"/>
-    <sheet name="아이템이름출력" sheetId="7" r:id="rId7"/>
-    <sheet name="유쾌한거래전인사" sheetId="9" r:id="rId8"/>
-    <sheet name="유쾌한거래후인사" sheetId="8" r:id="rId9"/>
-    <sheet name="아저씨거래전인사" sheetId="10" r:id="rId10"/>
-    <sheet name="아저씨거래후인사" sheetId="11" r:id="rId11"/>
+    <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
+    <sheet name="BreadShop_B" sheetId="13" r:id="rId2"/>
+    <sheet name="Tutorial_2" sheetId="23" r:id="rId3"/>
+    <sheet name="BreadShop_A" sheetId="22" r:id="rId4"/>
+    <sheet name="Tutorial_3" sheetId="16" r:id="rId5"/>
+    <sheet name="Bank" sheetId="17" r:id="rId6"/>
+    <sheet name="Blacksmith_B" sheetId="20" r:id="rId7"/>
+    <sheet name="Blacksmith_A" sheetId="24" r:id="rId8"/>
+    <sheet name="MerchantGuild_B" sheetId="18" r:id="rId9"/>
+    <sheet name="MerchantGuild_A" sheetId="25" r:id="rId10"/>
+    <sheet name="TownHall_B" sheetId="19" r:id="rId11"/>
+    <sheet name="TownHall_A" sheetId="26" r:id="rId12"/>
+    <sheet name="Tutorial_4" sheetId="21" r:id="rId13"/>
+    <sheet name="무뚝뚝거래전잡담" sheetId="3" r:id="rId14"/>
+    <sheet name="화난작별인사" sheetId="4" r:id="rId15"/>
+    <sheet name="무뚝뚝거래거절" sheetId="5" r:id="rId16"/>
+    <sheet name="유쾌한재흥정" sheetId="6" r:id="rId17"/>
+    <sheet name="아이템이름출력" sheetId="7" r:id="rId18"/>
+    <sheet name="유쾌한거래전인사" sheetId="9" r:id="rId19"/>
+    <sheet name="유쾌한거래후인사" sheetId="8" r:id="rId20"/>
+    <sheet name="아저씨거래전인사" sheetId="10" r:id="rId21"/>
+    <sheet name="아저씨거래후인사" sheetId="11" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="128">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -56,74 +67,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아리사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>빅터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안녕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>반가워</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오늘은 어때?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>괜찮은 것 같아</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다행이다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>별 걱정을 다 하네</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대화의 끝을 선언합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이게 무슨 막말 중인지 원.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트하기 위해서라고. 열심히 임할 것!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>에휴, 진짜.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예쁜 말 하기! 약속했잖아!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 정도면 나쁜 말 아니잖아?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SpeakerIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>벨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오, 무슨 얘기야?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>손님</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -240,6 +187,382 @@
   </si>
   <si>
     <t>그래도 [흥정제시가]골드보다는 잘 쳐줄순 없겠어? 당장 급해서말이야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>언니, 먼저 은행 가보자! 건물이 으리으리한 게 가보고 싶어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오 그거 좋은 생각! 이 마을에 은행이랑 길드 같은 건물들 있짆아. 어디부터 갈까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 음식은 안 먹어! 냄새만 맡을게! 언니, 시장 말고 중요한 건물들 먼저 둘러볼까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백호, 이 빵 냄새 맡아봐! 한 입 먹어볼래?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백호가 주인공의 어깨에 폴짝 올라타며 코를 킁킁거렸다. 큰 눈이 햇살을 받아 반짝이고, 리본 꼬리가 살랑였다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 넌 내 파트너야? 좋아, 백호! 같이 대박 나보자!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞아, 언니! 이 쿠퍼들은 이 마을의 무역 기운이 담긴 거야. 네 흥정 성공이 그 기운을 깨웠고, 그래서 내가 튀어나온 거지!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무역의 기운? 그게 뭐야? 은행 쿠퍼가 특별한 거였어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥, 귀엽다니 무례해! 난 백호. 초! 특! 급! 신비로운 무역 가이드야! 언니의 쿠퍼에 담긴 무역의 기운이 날 불렀지!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 뭐야, 이 귀여운 호랑이는 어디서 튀어나온 거지?! 내 흥정 봤다고?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>짜잔! 무역상 언니. 드디어 만났네! 방금 그 빵 흥정, 끝내줬어! 이 백호가 이제부터 든든하게 도와줄게!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠퍼가 부딪히는 소리 사이로 기묘한 기운이 퍼졌다. 빛이 점차 강해지며, 폴짝! 손바닥만 한 흰 호랑이 소녀가 튀어나왔다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이게 뭐지? 가방을 열었는데 왜 빛이 나는 거야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>또 다른 거래를 위해 가방을 여는 순간, 배낭 안에서 희미한 빛이 새어 나왔다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 또 다른 물건을 찾아볼까? 저기 과일 노점, 사과가 싱싱해 보여!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사는 빵을 하나 입에 물며 시장의 활기를 느꼈다. 첫 흥정 성공의 설렘이 가슴을 채웠다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보가 무역의 핵심이라던데, 아직은 좀 복잡하다. 그래도 하나씩 배우면서 다 해낼 거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사는 노점 간판을 꼼꼼히 읽으며 상인들의 대화를 귀 기울여 들었다. 메모장에 밀 가격과 시장 흐름을 기록했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사람들이 어떤 물건을 좋아하는지 알아내야 해. 내 밀은 어디서 제일 비싸게 팔 수 있을까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시장 노점엔 화려한 물건들이 가득했다. 붉은 향신료 항아리, 반짝이는 장신구, 신선한 채소와 생선이 눈을 사로잡았다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곡물, 생선, 향신료 냄새가 뒤섞여서 머리가 어지러울 정도야. 이곳에서 무역 시작하는 거, 진짜 멋지다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시장에는 햇살이 비치며 생기가 넘쳤다. 상인들의 호객 소리, 흥정 대화, 짐수레의 바퀴 굴러가는 소리가 어우러져 활력을 뿜어냈다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 돈으로 작은 거래부터 시작해서 점점 키울 거야. 첫 거래, 꼭 해낼 거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사는 낡은 가죽 배낭을 메고 시장의 소음 속에 섰다. 배낭 안에는 은행에서 빌린 돈과 품질 좋은 밀 자루가 들어 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀 늦게 뛰어들었지만, 지금부터 열심히 하면 다 따라잡을 수 있을 거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와, 이 시장 진짜 살아있네! 여기서 내 무역 모험이 시작될 거야! (너무 설렌다!)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘, 새로운 무역상이 시장 한복판에 섰다. 늦은 출발이었지만, 그녀의 눈빛은 뜨거운 의지로 불타올랐다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 마을의 시장은 그 꿈의 심장이었다. 햇살 아래 황금빛 밀 향기가 퍼지고, 상인들의 활기찬 외침이 골목을 메웠다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대무역시대의 웅장한 기운이 세상을 휘감았다. 바다를 가로지르는 상선과 대륙을 잇는 수레가 끊임없이 오갔다. 곡물, 향신료, 보석이 시장을 채우며, 모두가 부와 명예를 꿈꿨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사와 백호는 시장 한쪽에 자리한 은행 건물로 향했다. 단단한 돌문 위에 쿠퍼 모양이 새겨져 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사는 은행에서 빚 상환과 명성 시스템을 배우고, 무역의 큰 그림을 그렸다. 백호가 어깨에서 킥킥 웃었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고마워요, 언니! 다음엔 상환하고 명성도 쌓아서 올 거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하, 천천히 해도 괜찮아요. 명성 쌓고, 무역 성공해서 은행에서 자주 보자고요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행직원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상환은 아직 쿠퍼가 모자라서 나중에 다시 오도록 할게요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞아요, 대출 상환은 여기서 하면 돼요. 지금 상환할 쿠퍼 있으시면 기록할게요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요! 은행에서 쿠퍼를 빌렸는데, 여기서 상환하는 거 맞죠? 명성도 알려주세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요. 새 무역상이시죠? 여긴 은행이에요. 쿠퍼 대출을 관리하고, 빚을 상환하는 곳이죠. 돈은 저희가 언제나 안전하게 지키고 있습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행 안으로 들어서자, 은행원이 따뜻한 미소로 주인공을 맞이했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기가 은행이야! 뭔가 근사한 분위기네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사는 상인길드에서 퀘스트에 대해 알았다. 백호가 어깨에서 꼬리를 살랑였다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고마워, 아저씨! 다음엔 퀘스트 가지러 올게요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아, 기대할게! 퀘스트를 하다보면 자연스럽게 명성이 오를거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>길드원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이렇게 퀘스트 받는 거구나! 나중에 꼭 도전해볼게요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞아. 지금 준비가 부족해도 괜찮아. 언제든 수주할 수 있지.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응, 보여줘! 어디 어디… 와! 다양한 퀘스트가 있네?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕, 아가씨! 여긴 상인길드야. 퀘스트로 다른 마을에서 물건을 사오거나 거래하면 보상을 줘. 게시판에 뭐 있는지 볼래?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트? 완전 재밌어 보인다! 어떤 게 있는지 보여줘!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사와 백호는 시장 한쪽에 자리한 상인길드 건물로 향했다. 문 위엔 상선과 수레 문양이 새겨져 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백호가 어깨에서 킥킥 웃었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래! 잔뜩 쌓아서 오자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아! 잘해보는거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래할수록 유리해지는 거야? 명성 쌓아서 꼭 와봐야겠네!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞아! 명성이 높아지면 특정 물건에 대해 싸게 사거나 비싸게 팔 수 있을 거야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혜택이라면… 히히 물건을 좀 더 싸게 살 수 있다거나?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무역에서 물론 흥정도 중요하지만 더 중요한 건 명성이라고. 여기선 명성을 통해 여러 혜택들을 얻을 수 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기서는 뭘 하는거야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기는 마을회관이야, 언니!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사와 백호는 시장 한쪽에 자리한 마을회관으로 향했다. 건물은 화려한 문양으로 장식되어 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트 재밌어 보이지? 다음은 마을회관으로 가보자! 거기서 명성에 관해 알 수 있어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백호가 어깨에서 꼬리를 살랑거렸다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아, 언제든지 오거라.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대장장이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꼭 쿠퍼 모아서 다시 올게요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>짐칸을 더 큰 걸로 바꾸면 더 많은 물건을 들고 다닐 수 있을거다. 나중에 와서 교체해 봐.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요! 오늘은 구경왔어요. 아직 이것도 쓸만 하다고요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음, 손님인가? 여긴 대장간이다. 짐칸을 교체해서 용량을 늘릴 수 있지. 지금 필요한 게 있나?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>짐칸 늘리는 거? 완전 유용해 보이네! 잠깐 구경할까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여긴 대장간이야, 언니! 여기서 짐칸을 교체해서 더 많은 물건을 들고 다닐 수 있어. 무역할 때 짐칸 크기는 중요하거든!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사와 백호는 시장 한쪽에 자리한 대장간으로 향했다. 망치 소리가 울려 퍼졌다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사와 백호는 시장 끝쪽 노점을 향해 시선을 돌렸다. 햇살 아래 새로운 기회가 기다린다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나도 좋았어! 앞으로도 쭉쭉 거래하고 훌륭한 상인이 되는 거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백호, 오늘 하루 어땠어? 나는 너랑 같이 있어서 진짜 재밌었어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>언니, 초보치곤 잘했어! 어엿한 무역상 같았는걸?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백호, 오늘 하루 진짜 대박이었어! 물론 실패도 있었지만, 성공할 때 심장이 쿵쿵 뛰었어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사와 백호는 시장의 활기 속에서 돌아갔다. 햇살 아래 마을이 생기로 빛났다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아, 백호! 시장에서 더 큰 거래를 하자!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에도 좋은 거래 부탁해!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음에 또 봐요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사가 시장 소음에 익숙해질 무렵, 풍기는 빵 냄새에 이끌리듯 빵 가게 앞으로 향했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빵상인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕. 새 얼굴이네! 이 빵은 이 마을에서도 유명하다고. 80쿠퍼에 줄게. 어때, 살래?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 빵, 엄청 맛있어 보인다! 한 번 사볼까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미레사는 빵을 하나 입에 물며 시장의 활기를 느꼈다. 첫 거래 성공의 설렘이 가슴을 채웠다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래에서는 구매, 판매가 가장 기본이야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래 상대가 나한테 원하는 물건을 판매할 수도 있고, 내가 가지고 있는 것 중 원하는 것을 사려 할 수도 있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제시된 거래를 보고 거절할 지 받아드릴지 결정하면 돼. 그 과정에서 가격을 좀 흥정해볼 수도 있지!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아, 그럼 한 번 해볼까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 상인길드에 가보자! 거기서 퀘스트 받을 수 있어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>언니, 은행 언니 친절하네! 다음엔 대장간으로 가보자!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">언니, 마을회관도 끝! 이제 시장 돌아가서 거래하러 가자! </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeakIndex</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -286,12 +609,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -626,68 +946,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{379A5D65-0325-48BB-A201-E417E46FA241}">
-  <dimension ref="A1:C7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC3477D-A3C0-4737-B06F-046CAE216A66}">
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="17.375" customWidth="1"/>
-    <col min="3" max="3" width="70.125" customWidth="1"/>
+    <col min="1" max="1" width="12.75" customWidth="1"/>
+    <col min="3" max="3" width="185.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -695,37 +1005,237 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="C42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="C44" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="56" orientation="portrait" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="2" max="7" man="1"/>
+  </colBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4F457A-5250-4594-8189-F342AD0C6EEF}">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F635F0-DA45-4091-B7D9-D0E0BBF90D4B}">
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="101.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -739,21 +1249,84 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -763,13 +1336,527 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8924206-61AE-4D69-B844-8DAB6387AFF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE0F3A1D-3E43-40F3-BD59-BA7282E5D772}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="102.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3472BDDF-D772-45E0-98E4-F2FAB24EA68D}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="94.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A962835B-C748-46AD-8801-BF93978DA68F}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="101" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01630D74-A3BD-448E-8DB2-46783F003FC0}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD7361E-782F-4CC9-864F-19149DE85E4B}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7B0923-4B72-4CB5-94E5-4619DEBA32E5}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BEF320B-AE84-4C3F-B43E-2D8C1D71F14B}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF499146-2078-42CE-9B4B-33F785F2C86B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -783,10 +1870,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -794,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -805,10 +1892,76 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12050CB-2241-43EC-A575-1BA7884FCFB5}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -818,17 +1971,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65CF858-28DA-4B67-AF50-A2010BEF3C42}">
-  <dimension ref="A1:C8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB2C623-0C6E-4592-AD42-11937635DC8B}">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="3" max="3" width="60.375" customWidth="1"/>
+    <col min="3" max="3" width="83.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -839,79 +1991,175 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0F18A6-9C7B-45FA-A7D1-278EE75DDDD7}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4F457A-5250-4594-8189-F342AD0C6EEF}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8924206-61AE-4D69-B844-8DAB6387AFF9}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -921,13 +2169,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01630D74-A3BD-448E-8DB2-46783F003FC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{517303E9-EE3C-4973-B0A0-833CB9AB5621}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="101" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -941,21 +2192,21 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -963,21 +2214,21 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -987,13 +2238,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD7361E-782F-4CC9-864F-19149DE85E4B}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A709CA73-B878-4386-B9A8-89538A8412C9}">
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="90.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1007,10 +2261,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1018,32 +2272,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1053,13 +2285,16 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7B0923-4B72-4CB5-94E5-4619DEBA32E5}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56379732-A2C3-478C-9242-CDECB5FA3C88}">
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="104.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1070,13 +2305,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1084,21 +2316,18 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1106,10 +2335,144 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
-        <v>30</v>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1119,13 +2482,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BEF320B-AE84-4C3F-B43E-2D8C1D71F14B}">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB97AD4-5E41-4175-B7C8-ACD8E279A6C6}">
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="101.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1136,24 +2502,95 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1163,13 +2600,16 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF499146-2078-42CE-9B4B-33F785F2C86B}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F231014-875D-4FC2-9D05-164A4A201325}">
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="101" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1183,32 +2623,18 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1218,13 +2644,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12050CB-2241-43EC-A575-1BA7884FCFB5}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05049DA5-BEE8-48AA-9EBC-DFC10029C295}">
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="102.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1235,13 +2664,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1249,21 +2678,21 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1271,10 +2700,51 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1284,13 +2754,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0F18A6-9C7B-45FA-A7D1-278EE75DDDD7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B963174-88FD-4AB8-A36F-C80D4F3821B5}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="101" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1301,24 +2774,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HaveToTrade\Assets\Scripts\MG\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F21C48D-CD5E-4A66-8A73-FE109B5CEF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BA8C63-17ED-4ADF-957F-3FC3C497C18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="2895" windowWidth="15675" windowHeight="12450" firstSheet="9" activeTab="11" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
@@ -434,10 +434,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>퀘스트 재밌어 보이지? 다음은 마을회관으로 가보자! 거기서 명성에 관해 알 수 있어!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>백호가 어깨에서 꼬리를 살랑거렸다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -558,11 +554,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">언니, 마을회관도 끝! 이제 시장 돌아가서 거래하러 가자! </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SpeakIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">언니, 상인길드도 끝! 이제 시장 돌아가서 거래하러 가자! </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음은 마을회관으로 가보자! 거기서 명성에 관해 알 수 있어!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1235,7 +1235,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1389,7 +1389,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1546,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1568,7 +1568,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1579,7 +1579,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1590,7 +1590,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1994,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2002,10 +2002,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
         <v>116</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2016,7 +2016,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2195,7 +2195,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2206,7 +2206,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2217,7 +2217,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2228,7 +2228,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2261,10 +2261,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2275,7 +2275,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2308,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2521,7 +2521,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -2626,7 +2626,7 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2634,7 +2634,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2653,7 +2653,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2681,7 +2681,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2689,10 +2689,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2703,7 +2703,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2711,10 +2711,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2725,7 +2725,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2733,10 +2733,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2744,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2780,7 +2780,7 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\MG\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HaveToTrade\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BA8C63-17ED-4ADF-957F-3FC3C497C18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C25A00-53DC-4099-A82A-A0F9F60DB4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="4485" yWindow="2895" windowWidth="15675" windowHeight="12450" firstSheet="3" activeTab="4" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="129">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -563,6 +563,10 @@
   </si>
   <si>
     <t>다음은 마을회관으로 가보자! 거기서 명성에 관해 알 수 있어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오 그거 좋은 생각! 이 마을에 은행이랑 길드 같은 건물들 있잖아. 어디부터 갈까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2453,7 +2457,7 @@
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BA8C63-17ED-4ADF-957F-3FC3C497C18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17EC376-1D1B-4661-8C70-4597ED004430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="660" yWindow="660" windowWidth="13005" windowHeight="11385" firstSheet="3" activeTab="4" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="129">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -563,6 +563,10 @@
   </si>
   <si>
     <t>다음은 마을회관으로 가보자! 거기서 명성에 관해 알 수 있어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오 그거 좋은 생각! 이 마을에 은행이랑 길드 같은 건물들이 있잖아. 어디부터 갈까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2453,7 +2457,7 @@
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\MG\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HaveToTrade\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17EC376-1D1B-4661-8C70-4597ED004430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B647E5D4-E7D7-4DF1-A977-E6A8FFD45DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="660" windowWidth="13005" windowHeight="11385" firstSheet="3" activeTab="4" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="4485" yWindow="2895" windowWidth="15675" windowHeight="12450" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="127">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,10 +194,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오 그거 좋은 생각! 이 마을에 은행이랑 길드 같은 건물들 있짆아. 어디부터 갈까?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>인간 음식은 안 먹어! 냄새만 맡을게! 언니, 시장 말고 중요한 건물들 먼저 둘러볼까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -250,10 +246,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>미레사는 빵을 하나 입에 물며 시장의 활기를 느꼈다. 첫 흥정 성공의 설렘이 가슴을 채웠다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>정보가 무역의 핵심이라던데, 아직은 좀 복잡하다. 그래도 하나씩 배우면서 다 해낼 거야!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -566,7 +558,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오 그거 좋은 생각! 이 마을에 은행이랑 길드 같은 건물들이 있잖아. 어디부터 갈까?</t>
+    <t>오 그거 좋은 생각! 이 마을에 은행이랑 길드 같은 건물들 있잖아. 어디부터 갈까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -951,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC3477D-A3C0-4737-B06F-046CAE216A66}">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
@@ -974,7 +966,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -982,7 +974,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -990,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1001,7 +993,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1012,7 +1004,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1020,7 +1012,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1031,7 +1023,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1039,7 +1031,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1050,7 +1042,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1058,7 +1050,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1069,7 +1061,7 @@
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1077,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1088,135 +1080,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>0</v>
-      </c>
-      <c r="C31" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>0</v>
-      </c>
-      <c r="C33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>2</v>
-      </c>
-      <c r="C35" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>0</v>
-      </c>
-      <c r="C36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>2</v>
-      </c>
-      <c r="C37" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>0</v>
-      </c>
-      <c r="C38" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>2</v>
-      </c>
-      <c r="C39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>0</v>
-      </c>
-      <c r="C40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>0</v>
-      </c>
-      <c r="C42" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>2</v>
-      </c>
-      <c r="C43" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>0</v>
-      </c>
-      <c r="C44" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>2</v>
-      </c>
-      <c r="C45" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1239,7 +1103,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1256,7 +1120,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1264,10 +1128,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1278,7 +1142,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1286,10 +1150,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
         <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1300,7 +1164,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1308,10 +1172,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1322,7 +1186,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1330,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1363,10 +1227,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1374,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1393,7 +1257,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1407,10 +1271,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1421,7 +1285,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1429,10 +1293,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1443,7 +1307,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1451,10 +1315,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1465,7 +1329,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1473,10 +1337,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1487,7 +1351,7 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1495,7 +1359,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1528,10 +1392,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1542,7 +1406,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1550,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1561,7 +1425,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1569,10 +1433,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1583,7 +1447,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1591,10 +1455,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1602,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1998,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2006,10 +1870,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2020,7 +1884,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2199,7 +2063,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2210,7 +2074,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2221,7 +2085,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2232,7 +2096,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2265,10 +2129,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2279,7 +2143,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2312,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2323,7 +2187,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2331,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2342,7 +2206,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2350,7 +2214,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2358,10 +2222,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2372,7 +2236,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2380,10 +2244,10 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2394,7 +2258,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2402,10 +2266,10 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2416,7 +2280,7 @@
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2424,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2435,7 +2299,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2443,10 +2307,10 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2457,7 +2321,7 @@
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2465,7 +2329,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
         <v>34</v>
@@ -2476,7 +2340,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2509,10 +2373,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2520,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2528,10 +2392,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2542,7 +2406,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2550,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
         <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2564,7 +2428,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2572,10 +2436,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2586,7 +2450,7 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2594,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2627,10 +2491,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2638,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2657,7 +2521,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2671,10 +2535,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2685,7 +2549,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2693,10 +2557,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2707,7 +2571,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2715,10 +2579,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
         <v>97</v>
-      </c>
-      <c r="C6" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2729,7 +2593,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2737,10 +2601,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2748,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2781,10 +2645,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2792,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -1,40 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HaveToTrade\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B647E5D4-E7D7-4DF1-A977-E6A8FFD45DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1614B67-9205-4F6D-8F54-1D69F0594972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="2895" windowWidth="15675" windowHeight="12450" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="11865" yWindow="2070" windowWidth="15675" windowHeight="12450" activeTab="3" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
     <sheet name="BreadShop_B" sheetId="13" r:id="rId2"/>
     <sheet name="Tutorial_2" sheetId="23" r:id="rId3"/>
-    <sheet name="BreadShop_A" sheetId="22" r:id="rId4"/>
-    <sheet name="Tutorial_3" sheetId="16" r:id="rId5"/>
-    <sheet name="Bank" sheetId="17" r:id="rId6"/>
-    <sheet name="Blacksmith_B" sheetId="20" r:id="rId7"/>
-    <sheet name="Blacksmith_A" sheetId="24" r:id="rId8"/>
-    <sheet name="MerchantGuild_B" sheetId="18" r:id="rId9"/>
-    <sheet name="MerchantGuild_A" sheetId="25" r:id="rId10"/>
-    <sheet name="TownHall_B" sheetId="19" r:id="rId11"/>
-    <sheet name="TownHall_A" sheetId="26" r:id="rId12"/>
-    <sheet name="Tutorial_4" sheetId="21" r:id="rId13"/>
-    <sheet name="무뚝뚝거래전잡담" sheetId="3" r:id="rId14"/>
-    <sheet name="화난작별인사" sheetId="4" r:id="rId15"/>
-    <sheet name="무뚝뚝거래거절" sheetId="5" r:id="rId16"/>
-    <sheet name="유쾌한재흥정" sheetId="6" r:id="rId17"/>
-    <sheet name="아이템이름출력" sheetId="7" r:id="rId18"/>
-    <sheet name="유쾌한거래전인사" sheetId="9" r:id="rId19"/>
-    <sheet name="유쾌한거래후인사" sheetId="8" r:id="rId20"/>
-    <sheet name="아저씨거래전인사" sheetId="10" r:id="rId21"/>
-    <sheet name="아저씨거래후인사" sheetId="11" r:id="rId22"/>
+    <sheet name="Tutorial_3" sheetId="27" r:id="rId4"/>
+    <sheet name="BreadShop_A" sheetId="22" r:id="rId5"/>
+    <sheet name="Tutorial_4" sheetId="16" r:id="rId6"/>
+    <sheet name="Bank" sheetId="17" r:id="rId7"/>
+    <sheet name="Blacksmith_B" sheetId="20" r:id="rId8"/>
+    <sheet name="Blacksmith_A" sheetId="24" r:id="rId9"/>
+    <sheet name="MerchantGuild_B" sheetId="18" r:id="rId10"/>
+    <sheet name="MerchantGuild_A" sheetId="25" r:id="rId11"/>
+    <sheet name="TownHall_B" sheetId="19" r:id="rId12"/>
+    <sheet name="TownHall_A" sheetId="26" r:id="rId13"/>
+    <sheet name="Tutorial_5" sheetId="21" r:id="rId14"/>
+    <sheet name="무뚝뚝거래전잡담" sheetId="3" r:id="rId15"/>
+    <sheet name="화난작별인사" sheetId="4" r:id="rId16"/>
+    <sheet name="무뚝뚝거래거절" sheetId="5" r:id="rId17"/>
+    <sheet name="유쾌한재흥정" sheetId="6" r:id="rId18"/>
+    <sheet name="아이템이름출력" sheetId="7" r:id="rId19"/>
+    <sheet name="유쾌한거래전인사" sheetId="9" r:id="rId20"/>
+    <sheet name="유쾌한거래후인사" sheetId="8" r:id="rId21"/>
+    <sheet name="아저씨거래전인사" sheetId="10" r:id="rId22"/>
+    <sheet name="아저씨거래후인사" sheetId="11" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="138">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -438,14 +439,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>꼭 쿠퍼 모아서 다시 올게요!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>짐칸을 더 큰 걸로 바꾸면 더 많은 물건을 들고 다닐 수 있을거다. 나중에 와서 교체해 봐.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>안녕하세요! 오늘은 구경왔어요. 아직 이것도 쓸만 하다고요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -530,10 +523,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제시된 거래를 보고 거절할 지 받아드릴지 결정하면 돼. 그 과정에서 가격을 좀 흥정해볼 수도 있지!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>좋아, 그럼 한 번 해볼까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -559,6 +548,62 @@
   </si>
   <si>
     <t>오 그거 좋은 생각! 이 마을에 은행이랑 길드 같은 건물들 있잖아. 어디부터 갈까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미레사 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아, 우선 거래부터 해볼까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매나 판매 시에 원하는 개수로 조절하는 게 가능해.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아, 그런 식으로 내 현재 자금 상황에 맞게 끔 개수를 조절해야 돼.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 다음으로 거래에서 제일 중요한 요소! 흥정이야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥정은 현재 물품의 가격에서 구매 시에는 가격을 줄이고, 판매 시에는 가격을 늘릴 수 있는 수단이야</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥정 화면에서 본인이 원하는 값을 입력하고 흥정을 시도하면 돼!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다만 상대도 이윤이 있어야 하는 만큼 기존 가격과 너무 차이가 나면 당연히 거절할 확률이 높겠지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상대가 받아들일 수 있는 적절한 금액을 제시하는 게 핵심이야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 일단 구매해볼까? 빵이 먹고 싶어졌어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숫자 칸을 누르면 직접 값 입력도 가능해.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물품이 마음에 들지 않으면 거절해도 괜찮다는 점도 확인해두고…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>짐칸을 더 큰 걸로 바꾸면 더 많은 물건을 들고 다닐 수 있을거다. 자네가 명성을 쌓고 다닌다면 더 큰 짐칸에 대한 허가도 내려줄 수 있지.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아요! 다음에 찾아와서 꼭 바꿀게요!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -943,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC3477D-A3C0-4737-B06F-046CAE216A66}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.75" customWidth="1"/>
@@ -1081,6 +1126,17 @@
       </c>
       <c r="C14" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1094,6 +1150,50 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B963174-88FD-4AB8-A36F-C80D4F3821B5}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="101" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F635F0-DA45-4091-B7D9-D0E0BBF90D4B}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1103,7 +1203,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1203,7 +1303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE0F3A1D-3E43-40F3-BD59-BA7282E5D772}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1230,7 +1330,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1247,7 +1347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3472BDDF-D772-45E0-98E4-F2FAB24EA68D}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1257,7 +1357,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1368,7 +1468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A962835B-C748-46AD-8801-BF93978DA68F}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1395,7 +1495,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1406,7 +1506,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1414,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1425,7 +1525,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1436,7 +1536,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1447,7 +1547,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1458,7 +1558,7 @@
         <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1466,73 +1566,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01630D74-A3BD-448E-8DB2-46783F003FC0}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1542,7 +1576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD7361E-782F-4CC9-864F-19149DE85E4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01630D74-A3BD-448E-8DB2-46783F003FC0}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1559,46 +1593,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1642,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7B0923-4B72-4CB5-94E5-4619DEBA32E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD7361E-782F-4CC9-864F-19149DE85E4B}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1625,13 +1659,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1642,18 +1676,18 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1664,7 +1698,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1674,8 +1708,8 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BEF320B-AE84-4C3F-B43E-2D8C1D71F14B}">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7B0923-4B72-4CB5-94E5-4619DEBA32E5}">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1691,13 +1725,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1708,7 +1742,29 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1718,8 +1774,8 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF499146-2078-42CE-9B4B-33F785F2C86B}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BEF320B-AE84-4C3F-B43E-2D8C1D71F14B}">
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1735,13 +1791,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1752,18 +1808,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1773,8 +1818,8 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12050CB-2241-43EC-A575-1BA7884FCFB5}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF499146-2078-42CE-9B4B-33F785F2C86B}">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1790,13 +1835,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1807,29 +1852,18 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1843,6 +1877,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="3" max="3" width="83.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1862,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1870,10 +1905,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1884,7 +1919,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1894,8 +1929,8 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0F18A6-9C7B-45FA-A7D1-278EE75DDDD7}">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12050CB-2241-43EC-A575-1BA7884FCFB5}">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1917,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1928,7 +1963,29 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1938,7 +1995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4F457A-5250-4594-8189-F342AD0C6EEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0F18A6-9C7B-45FA-A7D1-278EE75DDDD7}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1955,24 +2012,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1982,6 +2039,50 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4F457A-5250-4594-8189-F342AD0C6EEF}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8924206-61AE-4D69-B844-8DAB6387AFF9}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2041,6 +2142,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="101" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2063,7 +2165,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2074,7 +2176,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2085,7 +2187,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2096,7 +2198,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2106,6 +2208,120 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CF94AF-60B5-4957-B853-09129F00AD6E}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="97.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A709CA73-B878-4386-B9A8-89538A8412C9}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2129,10 +2345,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2143,204 +2359,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56379732-A2C3-478C-9242-CDECB5FA3C88}">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="104.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2350,6 +2369,215 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56379732-A2C3-478C-9242-CDECB5FA3C88}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="104.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB97AD4-5E41-4175-B7C8-ACD8E279A6C6}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2467,7 +2695,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F231014-875D-4FC2-9D05-164A4A201325}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2494,7 +2722,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2502,117 +2730,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05049DA5-BEE8-48AA-9EBC-DFC10029C295}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="102.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2622,16 +2740,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B963174-88FD-4AB8-A36F-C80D4F3821B5}">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05049DA5-BEE8-48AA-9EBC-DFC10029C295}">
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="101" customWidth="1"/>
+    <col min="3" max="3" width="119.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2648,15 +2766,81 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HaveToTrade\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1614B67-9205-4F6D-8F54-1D69F0594972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348E2452-87C2-4B8E-8450-338AD97CF356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11865" yWindow="2070" windowWidth="15675" windowHeight="12450" activeTab="3" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="11865" yWindow="2070" windowWidth="15675" windowHeight="12450" activeTab="2" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="136">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -523,10 +523,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>좋아, 그럼 한 번 해볼까?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>다음은 상인길드에 가보자! 거기서 퀘스트 받을 수 있어!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -559,14 +555,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>구매나 판매 시에 원하는 개수로 조절하는 게 가능해.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>좋아, 그런 식으로 내 현재 자금 상황에 맞게 끔 개수를 조절해야 돼.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그럼 다음으로 거래에서 제일 중요한 요소! 흥정이야.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -591,10 +579,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>숫자 칸을 누르면 직접 값 입력도 가능해.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>물품이 마음에 들지 않으면 거절해도 괜찮다는 점도 확인해두고…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -604,6 +588,14 @@
   </si>
   <si>
     <t>좋아요! 다음에 찾아와서 꼭 바꿀게요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 버튼을 통해서 내가 살 물건의 개수를 조절하는 거야. 숫자 칸을 누르면 직접 값 입력도 가능해.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 버튼들을 눌러볼래?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1133,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" t="s">
         <v>124</v>
-      </c>
-      <c r="C15" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1176,7 +1168,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1203,7 +1195,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1330,7 +1322,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1357,7 +1349,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1495,7 +1487,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2139,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{517303E9-EE3C-4973-B0A0-833CB9AB5621}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
@@ -2187,18 +2179,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2209,7 +2190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CF94AF-60B5-4957-B853-09129F00AD6E}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -2235,7 +2216,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2243,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2257,7 +2238,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2268,7 +2249,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2279,7 +2260,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2290,7 +2271,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2301,18 +2282,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2404,7 +2374,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2549,7 +2519,7 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2722,7 +2692,7 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2749,7 +2719,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2810,7 +2780,7 @@
         <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2821,7 +2791,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HaveToTrade\Assets\Scripts\MG\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348E2452-87C2-4B8E-8450-338AD97CF356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867C64B5-BF7A-4777-B854-6C698F189216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11865" yWindow="2070" windowWidth="15675" windowHeight="12450" activeTab="2" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="19" activeTab="25" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
@@ -36,6 +36,9 @@
     <sheet name="유쾌한거래후인사" sheetId="8" r:id="rId21"/>
     <sheet name="아저씨거래전인사" sheetId="10" r:id="rId22"/>
     <sheet name="아저씨거래후인사" sheetId="11" r:id="rId23"/>
+    <sheet name="소년거래전인사" sheetId="28" r:id="rId24"/>
+    <sheet name="소년거래후인사" sheetId="29" r:id="rId25"/>
+    <sheet name="소년재흥정" sheetId="30" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="146">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -119,14 +122,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>하하, 이건 좀 비싸다, 아가씨! 좀 깎아줘야겠어!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">진짜요? 그럼 어떤 가격이 좋으신데요? </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(음…망했다…)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -596,6 +591,54 @@
   </si>
   <si>
     <t>이 버튼들을 눌러볼래?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요 누나!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어, 꼬마야. 무슨 일이니?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엄마가 심부름 시켜서요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네 누나! 이거면 될 것 같아요. 감사합니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음… 어떻게 할까..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응, 천천히 둘러보고 필요 한 게 있으면 말하렴.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래~ 다음에도 또 찾아오렴~!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 필요한 건 없니?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하, 아가씨, 조금만 잘 쳐 줄수 없겠어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엇, 그럼 이 가격은 어떨까요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[물건이름][주격조사] 이정도 가격은 아니라고 했는데.. 혹시 한번만 더 생각 해 줄 수 없을까요..?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1003,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1011,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1019,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1027,10 +1070,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1038,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1049,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1057,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1068,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1076,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1087,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1095,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1106,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1114,10 +1157,10 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1125,10 +1168,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1165,10 +1208,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1176,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1195,7 +1238,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1209,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1220,10 +1263,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1231,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1242,10 +1285,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" t="s">
         <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1253,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1264,10 +1307,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1275,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1286,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1319,10 +1362,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1330,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1349,7 +1392,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1363,10 +1406,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1374,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1385,10 +1428,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1396,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1407,10 +1450,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1418,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1429,10 +1472,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1440,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1451,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1484,10 +1527,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1495,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1506,7 +1549,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1514,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1525,10 +1568,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1536,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1547,10 +1590,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1558,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1588,15 +1631,15 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -1610,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -1618,7 +1661,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -1651,7 +1694,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1665,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -1673,7 +1716,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -1687,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1717,7 +1760,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1731,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -1739,7 +1782,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -1753,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -1783,13 +1826,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1797,10 +1840,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1833,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1841,10 +1884,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1855,7 +1898,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1889,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1897,10 +1940,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1908,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1938,13 +1981,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1952,21 +1995,21 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1974,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2004,13 +2047,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2018,10 +2061,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
         <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2051,10 +2094,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2065,7 +2108,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2141,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2106,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2120,7 +2163,172 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFE3197-89D6-4D0B-9F7C-347CC9D74981}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2875907-5E6F-4393-8BB5-A18A32B4E07F}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4097B36D-6908-477D-9E49-52F3965E6275}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2154,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2165,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2176,10 +2384,10 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2213,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2224,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2235,10 +2443,10 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2246,10 +2454,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2257,10 +2465,10 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2268,10 +2476,10 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2279,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2315,10 +2523,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2326,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2363,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2371,10 +2579,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2382,10 +2590,10 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2393,7 +2601,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2401,10 +2609,10 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2412,7 +2620,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2420,10 +2628,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2431,10 +2639,10 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2442,10 +2650,10 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2453,10 +2661,10 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2464,10 +2672,10 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2475,10 +2683,10 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2486,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2494,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2505,10 +2713,10 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2516,10 +2724,10 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2527,10 +2735,10 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2538,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2571,10 +2779,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2582,7 +2790,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2590,10 +2798,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2601,10 +2809,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2612,10 +2820,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
         <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2623,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2634,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2645,10 +2853,10 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2656,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2689,10 +2897,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2700,7 +2908,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2719,7 +2927,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -2733,10 +2941,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2744,10 +2952,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2755,10 +2963,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
         <v>95</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2766,10 +2974,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2777,10 +2985,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2788,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2799,10 +3007,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2810,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Scripts/MG/Data/DialogData.xlsx
+++ b/Assets/Scripts/MG/Data/DialogData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\MG\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867C64B5-BF7A-4777-B854-6C698F189216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807C6DE1-3A20-4603-901D-93E095DE2916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="19" activeTab="25" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="21" activeTab="27" xr2:uid="{7E573E84-A36E-4879-9C52-4355E21305E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial_1" sheetId="12" r:id="rId1"/>
@@ -39,6 +39,8 @@
     <sheet name="소년거래전인사" sheetId="28" r:id="rId24"/>
     <sheet name="소년거래후인사" sheetId="29" r:id="rId25"/>
     <sheet name="소년재흥정" sheetId="30" r:id="rId26"/>
+    <sheet name="상인구매흥정오류" sheetId="31" r:id="rId27"/>
+    <sheet name="상인판매흥정오류" sheetId="32" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="148">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -639,6 +641,14 @@
   </si>
   <si>
     <t>[물건이름][주격조사] 이정도 가격은 아니라고 했는데.. 혹시 한번만 더 생각 해 줄 수 없을까요..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음... 요즘 여행을 많이 했더니 피곤했나..? 왜 이걸 이렇게 비싸게 사려고 했지..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나 참, 상인인데도 돈에 음수가 있다는 엉뚱한 생각을 가끔 하게된단말이지~</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2337,6 +2347,72 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6283F43-E535-4654-BF2B-05B21063A64A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DCB15C2-A2E8-408F-A10E-477C009F3C45}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{517303E9-EE3C-4973-B0A0-833CB9AB5621}">
   <dimension ref="A1:C4"/>
